--- a/public/outils/matrices/dcf-valorisation.xlsx
+++ b/public/outils/matrices/dcf-valorisation.xlsx
@@ -52,7 +52,7 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <i val="1"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF6C5AB0"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
@@ -74,7 +74,7 @@
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF6C5AB0"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -133,19 +133,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF44546A"/>
+        <fgColor rgb="FF4B3D7C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
+        <fgColor rgb="FFF1EEF8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8497B0"/>
+        <fgColor rgb="FF8B7CC4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -163,24 +163,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B9BD5"/>
+        <fgColor rgb="FF6C5AB0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9BC2E6"/>
+        <fgColor rgb="FFC9C0E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF44546A"/>
+        <fgColor rgb="FF4B3D7C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8497B0"/>
+        <fgColor rgb="FF8B7CC4"/>
       </patternFill>
     </fill>
   </fills>
@@ -384,6 +384,72 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="8953500" y="7270750"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8953500" y="7270750"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="7534275" y="387350"/>
+    <xdr:ext cx="1685925" cy="419100"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Logo CorpusImmo" descr="CorpusImmo, www.corpus.immo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7534275" y="387350"/>
+          <a:ext cx="1685925" cy="419100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -702,7 +768,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -720,14 +786,14 @@
     <row r="1" ht="18.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MATRICE DCF IMMOBILIER — MODÈLE RÉUTILISABLE</t>
+          <t>MATRICE DCF IMMOBILIER : MODÈLE RÉUTILISABLE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ne saisir que les cellules BLEUES. Tout le reste est calculé — ne rien écraser.</t>
+          <t>Ne saisir que les cellules VIOLETTES. Tout le reste est calculé, ne rien écraser.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1793,7 +1859,7 @@
     <row r="34">
       <c r="D34" s="31" t="inlineStr">
         <is>
-          <t>Bleu = à saisir par l'utilisateur</t>
+          <t>Violet = à saisir par l'utilisateur</t>
         </is>
       </c>
     </row>
@@ -1910,11 +1976,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2121,5 +2188,6 @@
     <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/outils/matrices/dcf-valorisation.xlsx
+++ b/public/outils/matrices/dcf-valorisation.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Rappel acquisition — Prix HD</t>
+          <t>Rappel acquisition : Prix HD</t>
         </is>
       </c>
       <c r="E10" s="16">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Rappel acquisition — Droits</t>
+          <t>Rappel acquisition : Droits</t>
         </is>
       </c>
       <c r="E11" s="16">
@@ -1151,7 +1151,7 @@
     <row r="12">
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Rappel acquisition — Fonds propres (= flux période 0)</t>
+          <t>Rappel acquisition : Fonds propres (= flux période 0)</t>
         </is>
       </c>
       <c r="E12" s="16">
@@ -1795,7 +1795,7 @@
       <c r="B30" s="6" t="n"/>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>Contrôle — % surface relouée (doit être ≤ 100%)</t>
+          <t>Contrôle : % surface relouée (doit être ≤ 100%)</t>
         </is>
       </c>
       <c r="E30" s="28">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>Contrôle — % capex engagé (doit être = 100%)</t>
+          <t>Contrôle : % capex engagé (doit être = 100%)</t>
         </is>
       </c>
       <c r="E31" s="28">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>Contrôle — horizon de détention (doit être entre 1 et 7)</t>
+          <t>Contrôle : horizon de détention (doit être entre 1 et 7)</t>
         </is>
       </c>
       <c r="E32" s="8">
@@ -1996,7 +1996,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="32" t="inlineStr">
         <is>
-          <t>MATRICE DCF IMMOBILIER — MÉTHODE, CONVENTIONS ET LIMITES</t>
+          <t>MATRICE DCF IMMOBILIER : MÉTHODE, CONVENTIONS ET LIMITES</t>
         </is>
       </c>
       <c r="B1" s="32" t="n"/>
@@ -2131,7 +2131,7 @@
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>— Il ne gère aucune échéance de bail : le loyer en place est supposé courir et s'indexer sur tout l'horizon, sans break ni expiration. Sur un actif tertiaire, c'est la simplification la plus lourde du modèle.</t>
+          <t>· Il ne gère aucune échéance de bail : le loyer en place est supposé courir et s'indexer sur tout l'horizon, sans break ni expiration. Sur un actif tertiaire, c'est la simplification la plus lourde du modèle.</t>
         </is>
       </c>
       <c r="B17" s="36" t="n"/>
@@ -2139,7 +2139,7 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="36" t="inlineStr">
         <is>
-          <t>— Il n'intègre ni fiscalité, ni impôt sur les sociétés, ni frais de structure ou d'asset management.</t>
+          <t>· Il n'intègre ni fiscalité, ni impôt sur les sociétés, ni frais de structure ou d'asset management.</t>
         </is>
       </c>
       <c r="B18" s="36" t="n"/>
@@ -2147,7 +2147,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="36" t="inlineStr">
         <is>
-          <t>— Il ne traite ni les baux à paliers, ni les loyers variables, ni le détail des refacturations de charges.</t>
+          <t>· Il ne traite ni les baux à paliers, ni les loyers variables, ni le détail des refacturations de charges.</t>
         </is>
       </c>
       <c r="B19" s="36" t="n"/>
@@ -2155,7 +2155,7 @@
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="36" t="inlineStr">
         <is>
-          <t>— Il ne remplace pas une due diligence : état locatif réel, audit technique, urbanisme et environnement restent hors champ.</t>
+          <t>· Il ne remplace pas une due diligence : état locatif réel, audit technique, urbanisme et environnement restent hors champ.</t>
         </is>
       </c>
       <c r="B20" s="36" t="n"/>
@@ -2163,7 +2163,7 @@
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>— L'horizon est limité à 7 périodes. Au-delà, aucune cession n'est simulée : la saisie est bloquée et un contrôle le signale.</t>
+          <t>· L'horizon est limité à 7 périodes. Au-delà, aucune cession n'est simulée : la saisie est bloquée et un contrôle le signale.</t>
         </is>
       </c>
       <c r="B21" s="36" t="n"/>
